--- a/data/derived_data/4_Diversities/ps_ITS_rare_expe_D1_20_tax_table.xlsx
+++ b/data/derived_data/4_Diversities/ps_ITS_rare_expe_D1_20_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="463">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -74,6 +74,9 @@
     <t xml:space="preserve">Dipodascaceae</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_10</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unknown</t>
   </si>
   <si>
@@ -134,6 +137,9 @@
     <t xml:space="preserve">Cluster_1016</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_1016</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_103</t>
   </si>
   <si>
@@ -158,6 +164,9 @@
     <t xml:space="preserve">Cluster_1055</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_1055</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_1066</t>
   </si>
   <si>
@@ -176,12 +185,18 @@
     <t xml:space="preserve">Cluster_107</t>
   </si>
   <si>
+    <t xml:space="preserve">pulcherrima</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_108</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_109</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_109</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_11</t>
   </si>
   <si>
@@ -212,6 +227,9 @@
     <t xml:space="preserve">Cluster_1126</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_1126</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_113</t>
   </si>
   <si>
@@ -296,6 +314,9 @@
     <t xml:space="preserve">Sporidiobolales</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_129</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_13</t>
   </si>
   <si>
@@ -350,6 +371,9 @@
     <t xml:space="preserve">Cluster_158</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_158</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_159</t>
   </si>
   <si>
@@ -371,9 +395,15 @@
     <t xml:space="preserve">Cluster_163</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_163</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_165</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_165</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_166</t>
   </si>
   <si>
@@ -395,6 +425,9 @@
     <t xml:space="preserve">Cluster_176</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_176</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_177</t>
   </si>
   <si>
@@ -425,6 +458,9 @@
     <t xml:space="preserve">Cluster_179</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_179</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_18</t>
   </si>
   <si>
@@ -437,9 +473,15 @@
     <t xml:space="preserve">Cluster_180</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_180</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_182</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_182</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_186</t>
   </si>
   <si>
@@ -482,6 +524,9 @@
     <t xml:space="preserve">Cluster_199</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_199</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_2</t>
   </si>
   <si>
@@ -506,6 +551,9 @@
     <t xml:space="preserve">Cluster_21</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_21</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_212</t>
   </si>
   <si>
@@ -524,6 +572,9 @@
     <t xml:space="preserve">Microstromatales</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_215</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_216</t>
   </si>
   <si>
@@ -536,12 +587,33 @@
     <t xml:space="preserve">Cluster_222</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_222</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_231</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_240</t>
   </si>
   <si>
+    <t xml:space="preserve">Viridiplantae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streptophyta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnoliopsida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rubus</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_242</t>
   </si>
   <si>
@@ -560,6 +632,9 @@
     <t xml:space="preserve">Cluster_251</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_251</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_257</t>
   </si>
   <si>
@@ -617,6 +692,9 @@
     <t xml:space="preserve">Symmetrosporaceae</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_281</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_289</t>
   </si>
   <si>
@@ -719,6 +797,9 @@
     <t xml:space="preserve">Cluster_34</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_34</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_340</t>
   </si>
   <si>
@@ -773,12 +854,21 @@
     <t xml:space="preserve">Cluster_368</t>
   </si>
   <si>
+    <t xml:space="preserve">Martiniozyma</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_37</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_371</t>
   </si>
   <si>
+    <t xml:space="preserve">Prunus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avium</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_375</t>
   </si>
   <si>
@@ -797,6 +887,9 @@
     <t xml:space="preserve">Cluster_391</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_391</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_394</t>
   </si>
   <si>
@@ -806,6 +899,9 @@
     <t xml:space="preserve">Sclerotiniaceae</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_41</t>
   </si>
   <si>
@@ -863,12 +959,21 @@
     <t xml:space="preserve">Cluster_43</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_43</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_436</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_436</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_438</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_438</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_44</t>
   </si>
   <si>
@@ -887,6 +992,9 @@
     <t xml:space="preserve">Cluster_465</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_465</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_49</t>
   </si>
   <si>
@@ -902,6 +1010,9 @@
     <t xml:space="preserve">Cluster_51</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_51</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_52</t>
   </si>
   <si>
@@ -926,12 +1037,18 @@
     <t xml:space="preserve">Cluster_540</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_540</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_55</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_557</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_557</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_56</t>
   </si>
   <si>
@@ -944,6 +1061,9 @@
     <t xml:space="preserve">Cluster_576</t>
   </si>
   <si>
+    <t xml:space="preserve">sulcatus</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_58</t>
   </si>
   <si>
@@ -968,6 +1088,9 @@
     <t xml:space="preserve">Cluster_6</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_6</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_602</t>
   </si>
   <si>
@@ -977,12 +1100,21 @@
     <t xml:space="preserve">Cluster_604</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_604</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_61</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_61</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_612</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_612</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_615</t>
   </si>
   <si>
@@ -995,15 +1127,24 @@
     <t xml:space="preserve">Cluster_626</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_626</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_628</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_628</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_63</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_639</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_639</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_64</t>
   </si>
   <si>
@@ -1013,6 +1154,9 @@
     <t xml:space="preserve">Cluster_66</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_66</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_67</t>
   </si>
   <si>
@@ -1040,9 +1184,6 @@
     <t xml:space="preserve">Cluster_72</t>
   </si>
   <si>
-    <t xml:space="preserve">Cluster_729</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_73</t>
   </si>
   <si>
@@ -1064,15 +1205,42 @@
     <t xml:space="preserve">Cluster_744</t>
   </si>
   <si>
+    <t xml:space="preserve">avinus</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_760</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_760</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_769</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_77</t>
   </si>
   <si>
+    <t xml:space="preserve">Chromista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oomycota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peronosporomycetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peronosporales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peronosporaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phytophthora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cactorum</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_778</t>
   </si>
   <si>
@@ -1103,6 +1271,9 @@
     <t xml:space="preserve">Cluster_81</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_81</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_819</t>
   </si>
   <si>
@@ -1136,15 +1307,24 @@
     <t xml:space="preserve">Cluster_848</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_848</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_87</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_871</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_871</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_88</t>
   </si>
   <si>
+    <t xml:space="preserve">Unknown_88</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_886</t>
   </si>
   <si>
@@ -1178,10 +1358,16 @@
     <t xml:space="preserve">Cluster_895</t>
   </si>
   <si>
+    <t xml:space="preserve">pimensis</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_9</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown_912</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_92</t>
@@ -1618,12 +1804,12 @@
         <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -1635,21 +1821,21 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -1658,76 +1844,76 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -1736,76 +1922,76 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -1814,128 +2000,128 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" t="s">
         <v>54</v>
       </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" t="s">
-        <v>51</v>
-      </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H15" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -1947,21 +2133,21 @@
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
@@ -1973,73 +2159,73 @@
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H17" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="G18" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H19" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
@@ -2051,21 +2237,21 @@
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H20" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
@@ -2077,47 +2263,47 @@
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H21" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F22" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
@@ -2138,64 +2324,64 @@
         <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G24" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
@@ -2207,21 +2393,21 @@
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
@@ -2230,50 +2416,50 @@
         <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F27" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G27" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G28" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="H28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
@@ -2285,21 +2471,21 @@
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H29" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
@@ -2308,24 +2494,24 @@
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F30" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G30" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H30" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
@@ -2334,50 +2520,50 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F31" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G31" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="H31" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E32" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F32" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
@@ -2386,24 +2572,24 @@
         <v>10</v>
       </c>
       <c r="D33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E33" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F33" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G33" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
@@ -2415,21 +2601,21 @@
         <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H34" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
@@ -2441,47 +2627,47 @@
         <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H35" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E36" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G36" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="H36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
@@ -2490,24 +2676,24 @@
         <v>10</v>
       </c>
       <c r="D37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E37" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F37" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="G37" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H37" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
@@ -2516,50 +2702,50 @@
         <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E38" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F38" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G38" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H38" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F39" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="G39" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="H39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
@@ -2568,50 +2754,50 @@
         <v>10</v>
       </c>
       <c r="D40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E40" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F40" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G40" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="H40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F41" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B42" t="s">
         <v>9</v>
@@ -2623,21 +2809,21 @@
         <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G42" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B43" t="s">
         <v>9</v>
@@ -2646,24 +2832,24 @@
         <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E43" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F43" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G43" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="H43" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
@@ -2672,24 +2858,24 @@
         <v>10</v>
       </c>
       <c r="D44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E44" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F44" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="G44" t="s">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="H44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
@@ -2698,76 +2884,76 @@
         <v>10</v>
       </c>
       <c r="D45" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E45" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F45" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G45" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H45" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
       </c>
       <c r="C46" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D46" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E46" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F46" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="G46" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="H46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B47" t="s">
         <v>9</v>
       </c>
       <c r="C47" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D47" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E47" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F47" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="G47" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="H47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B48" t="s">
         <v>9</v>
@@ -2776,102 +2962,102 @@
         <v>10</v>
       </c>
       <c r="D48" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E48" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F48" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G48" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="H48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B49" t="s">
         <v>9</v>
       </c>
       <c r="C49" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D49" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="G49" t="s">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="H49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B50" t="s">
         <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="G50" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="H50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="B51" t="s">
         <v>9</v>
       </c>
       <c r="C51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E51" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F51" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="B52" t="s">
         <v>9</v>
@@ -2880,24 +3066,24 @@
         <v>10</v>
       </c>
       <c r="D52" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E52" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F52" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G52" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H52" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="B53" t="s">
         <v>9</v>
@@ -2906,24 +3092,24 @@
         <v>10</v>
       </c>
       <c r="D53" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E53" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F53" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G53" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="H53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B54" t="s">
         <v>9</v>
@@ -2932,24 +3118,24 @@
         <v>10</v>
       </c>
       <c r="D54" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E54" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F54" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G54" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H54" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="B55" t="s">
         <v>9</v>
@@ -2958,24 +3144,24 @@
         <v>10</v>
       </c>
       <c r="D55" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E55" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F55" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G55" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="H55" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
@@ -2984,50 +3170,50 @@
         <v>10</v>
       </c>
       <c r="D56" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E56" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F56" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G56" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H56" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="B57" t="s">
         <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D57" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E57" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="G57" t="s">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="H57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="B58" t="s">
         <v>9</v>
@@ -3053,7 +3239,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
@@ -3065,21 +3251,21 @@
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H59" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="B60" t="s">
         <v>9</v>
@@ -3088,24 +3274,24 @@
         <v>10</v>
       </c>
       <c r="D60" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E60" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F60" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="G60" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="H60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B61" t="s">
         <v>9</v>
@@ -3123,119 +3309,119 @@
         <v>19</v>
       </c>
       <c r="G61" t="s">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="H61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D62" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E62" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F62" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G62" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="B63" t="s">
         <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D63" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E63" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F63" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G63" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H63" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B64" t="s">
         <v>9</v>
       </c>
       <c r="C64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D64" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E64" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="F64" t="s">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="G64" t="s">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="H64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="B65" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F65" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G65" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="B66" t="s">
         <v>9</v>
@@ -3244,102 +3430,102 @@
         <v>10</v>
       </c>
       <c r="D66" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E66" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F66" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="G66" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="H66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="B67" t="s">
         <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D67" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E67" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F67" t="s">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="G67" t="s">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="H67" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="B68" t="s">
         <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D68" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E68" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F68" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G68" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H68" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B69" t="s">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="C69" t="s">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="D69" t="s">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="E69" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="F69" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="G69" t="s">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="H69" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="B70" t="s">
         <v>9</v>
@@ -3351,21 +3537,21 @@
         <v>11</v>
       </c>
       <c r="E70" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G70" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="B71" t="s">
         <v>9</v>
@@ -3374,24 +3560,24 @@
         <v>10</v>
       </c>
       <c r="D71" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E71" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F71" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G71" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H71" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="B72" t="s">
         <v>9</v>
@@ -3403,99 +3589,99 @@
         <v>11</v>
       </c>
       <c r="E72" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G72" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H72" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="B73" t="s">
         <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D73" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E73" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F73" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G73" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H73" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="B74" t="s">
         <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F74" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="G74" t="s">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="H74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="B75" t="s">
         <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D75" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E75" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F75" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G75" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="H75" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="B76" t="s">
         <v>9</v>
@@ -3504,50 +3690,50 @@
         <v>10</v>
       </c>
       <c r="D76" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F76" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="G76" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="H76" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="B77" t="s">
         <v>9</v>
       </c>
       <c r="C77" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D77" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E77" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F77" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G77" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="B78" t="s">
         <v>9</v>
@@ -3556,50 +3742,50 @@
         <v>10</v>
       </c>
       <c r="D78" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E78" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F78" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G78" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="B79" t="s">
         <v>9</v>
       </c>
       <c r="C79" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D79" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E79" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F79" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G79" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="B80" t="s">
         <v>9</v>
@@ -3611,21 +3797,21 @@
         <v>11</v>
       </c>
       <c r="E80" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G80" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H80" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="B81" t="s">
         <v>9</v>
@@ -3634,24 +3820,24 @@
         <v>10</v>
       </c>
       <c r="D81" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E81" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F81" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G81" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H81" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="B82" t="s">
         <v>9</v>
@@ -3663,21 +3849,21 @@
         <v>11</v>
       </c>
       <c r="E82" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G82" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H82" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="B83" t="s">
         <v>9</v>
@@ -3689,99 +3875,99 @@
         <v>11</v>
       </c>
       <c r="E83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G83" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H83" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="B84" t="s">
         <v>9</v>
       </c>
       <c r="C84" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D84" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="E84" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="F84" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="G84" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="H84" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="B85" t="s">
         <v>9</v>
       </c>
       <c r="C85" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D85" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="E85" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F85" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="G85" t="s">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="H85" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="B86" t="s">
         <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D86" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E86" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F86" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="G86" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="H86" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="B87" t="s">
         <v>9</v>
@@ -3790,24 +3976,24 @@
         <v>10</v>
       </c>
       <c r="D87" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E87" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F87" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G87" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H87" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="B88" t="s">
         <v>9</v>
@@ -3816,50 +4002,50 @@
         <v>10</v>
       </c>
       <c r="D88" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E88" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F88" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G88" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H88" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="B89" t="s">
         <v>9</v>
       </c>
       <c r="C89" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D89" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="E89" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="F89" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="G89" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="H89" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="B90" t="s">
         <v>9</v>
@@ -3868,24 +4054,24 @@
         <v>10</v>
       </c>
       <c r="D90" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E90" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="F90" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="G90" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="H90" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="B91" t="s">
         <v>9</v>
@@ -3906,12 +4092,12 @@
         <v>14</v>
       </c>
       <c r="H91" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="B92" t="s">
         <v>9</v>
@@ -3920,76 +4106,76 @@
         <v>10</v>
       </c>
       <c r="D92" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E92" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F92" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G92" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H92" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="B93" t="s">
         <v>9</v>
       </c>
       <c r="C93" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D93" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E93" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F93" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="G93" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="H93" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="B94" t="s">
         <v>9</v>
       </c>
       <c r="C94" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D94" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E94" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F94" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G94" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H94" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="B95" t="s">
         <v>9</v>
@@ -4001,73 +4187,73 @@
         <v>11</v>
       </c>
       <c r="E95" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G95" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H95" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="B96" t="s">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="C96" t="s">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="D96" t="s">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="E96" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="F96" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="G96" t="s">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="H96" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="B97" t="s">
         <v>9</v>
       </c>
       <c r="C97" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D97" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="E97" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="F97" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="G97" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="H97" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="B98" t="s">
         <v>9</v>
@@ -4079,21 +4265,21 @@
         <v>11</v>
       </c>
       <c r="E98" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F98" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G98" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H98" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="B99" t="s">
         <v>9</v>
@@ -4105,47 +4291,47 @@
         <v>11</v>
       </c>
       <c r="E99" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F99" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G99" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H99" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="B100" t="s">
         <v>9</v>
       </c>
       <c r="C100" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D100" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E100" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F100" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G100" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H100" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="B101" t="s">
         <v>9</v>
@@ -4154,50 +4340,50 @@
         <v>10</v>
       </c>
       <c r="D101" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E101" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F101" t="s">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="G101" t="s">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="H101" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="B102" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C102" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D102" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E102" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F102" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G102" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H102" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="B103" t="s">
         <v>9</v>
@@ -4206,24 +4392,24 @@
         <v>10</v>
       </c>
       <c r="D103" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E103" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F103" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G103" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H103" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="B104" t="s">
         <v>9</v>
@@ -4232,24 +4418,24 @@
         <v>10</v>
       </c>
       <c r="D104" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="E104" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="F104" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="G104" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="H104" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="B105" t="s">
         <v>9</v>
@@ -4261,99 +4447,99 @@
         <v>11</v>
       </c>
       <c r="E105" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G105" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H105" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="B106" t="s">
         <v>9</v>
       </c>
       <c r="C106" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D106" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E106" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F106" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="G106" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="H106" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="B107" t="s">
         <v>9</v>
       </c>
       <c r="C107" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D107" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="E107" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="F107" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="G107" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="H107" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="B108" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C108" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D108" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E108" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F108" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G108" t="s">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="H108" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="B109" t="s">
         <v>9</v>
@@ -4365,73 +4551,73 @@
         <v>11</v>
       </c>
       <c r="E109" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G109" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H109" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="B110" t="s">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="C110" t="s">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="D110" t="s">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="E110" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="F110" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="G110" t="s">
-        <v>20</v>
+        <v>283</v>
       </c>
       <c r="H110" t="s">
-        <v>20</v>
+        <v>284</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="B111" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C111" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D111" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E111" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F111" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G111" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H111" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="B112" t="s">
         <v>9</v>
@@ -4443,21 +4629,21 @@
         <v>11</v>
       </c>
       <c r="E112" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F112" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G112" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H112" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="B113" t="s">
         <v>9</v>
@@ -4469,21 +4655,21 @@
         <v>11</v>
       </c>
       <c r="E113" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F113" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G113" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H113" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="B114" t="s">
         <v>9</v>
@@ -4492,24 +4678,24 @@
         <v>10</v>
       </c>
       <c r="D114" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E114" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F114" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G114" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H114" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="B115" t="s">
         <v>9</v>
@@ -4518,76 +4704,76 @@
         <v>10</v>
       </c>
       <c r="D115" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E115" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F115" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G115" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H115" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="B116" t="s">
         <v>9</v>
       </c>
       <c r="C116" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D116" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E116" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F116" t="s">
-        <v>20</v>
+        <v>291</v>
       </c>
       <c r="G116" t="s">
-        <v>20</v>
+        <v>291</v>
       </c>
       <c r="H116" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="B117" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C117" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D117" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E117" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F117" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G117" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H117" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="B118" t="s">
         <v>9</v>
@@ -4596,24 +4782,24 @@
         <v>10</v>
       </c>
       <c r="D118" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E118" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F118" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="G118" t="s">
-        <v>20</v>
+        <v>295</v>
       </c>
       <c r="H118" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="B119" t="s">
         <v>9</v>
@@ -4622,102 +4808,102 @@
         <v>10</v>
       </c>
       <c r="D119" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E119" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F119" t="s">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="G119" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="H119" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="B120" t="s">
         <v>9</v>
       </c>
       <c r="C120" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D120" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="E120" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="F120" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="G120" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="H120" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="B121" t="s">
         <v>9</v>
       </c>
       <c r="C121" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="D121" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="E121" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="F121" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="G121" t="s">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="H121" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="B122" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C122" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D122" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E122" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F122" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G122" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H122" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="B123" t="s">
         <v>9</v>
@@ -4726,24 +4912,24 @@
         <v>10</v>
       </c>
       <c r="D123" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E123" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F123" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G123" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H123" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="B124" t="s">
         <v>9</v>
@@ -4752,24 +4938,24 @@
         <v>10</v>
       </c>
       <c r="D124" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="E124" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="F124" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="G124" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="H124" t="s">
-        <v>281</v>
+        <v>313</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="B125" t="s">
         <v>9</v>
@@ -4778,76 +4964,76 @@
         <v>10</v>
       </c>
       <c r="D125" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E125" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F125" t="s">
-        <v>20</v>
+        <v>315</v>
       </c>
       <c r="G125" t="s">
-        <v>20</v>
+        <v>315</v>
       </c>
       <c r="H125" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="B126" t="s">
         <v>9</v>
       </c>
       <c r="C126" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D126" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E126" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F126" t="s">
-        <v>20</v>
+        <v>317</v>
       </c>
       <c r="G126" t="s">
-        <v>20</v>
+        <v>317</v>
       </c>
       <c r="H126" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="B127" t="s">
         <v>9</v>
       </c>
       <c r="C127" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D127" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E127" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F127" t="s">
-        <v>20</v>
+        <v>319</v>
       </c>
       <c r="G127" t="s">
-        <v>20</v>
+        <v>319</v>
       </c>
       <c r="H127" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="B128" t="s">
         <v>9</v>
@@ -4856,24 +5042,24 @@
         <v>10</v>
       </c>
       <c r="D128" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E128" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F128" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G128" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H128" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="B129" t="s">
         <v>9</v>
@@ -4885,47 +5071,47 @@
         <v>11</v>
       </c>
       <c r="E129" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F129" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G129" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H129" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>287</v>
+        <v>322</v>
       </c>
       <c r="B130" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D130" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E130" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F130" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G130" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H130" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
       <c r="B131" t="s">
         <v>9</v>
@@ -4937,21 +5123,21 @@
         <v>11</v>
       </c>
       <c r="E131" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F131" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G131" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H131" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="B132" t="s">
         <v>9</v>
@@ -4960,76 +5146,76 @@
         <v>10</v>
       </c>
       <c r="D132" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E132" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F132" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G132" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H132" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>290</v>
+        <v>325</v>
       </c>
       <c r="B133" t="s">
         <v>9</v>
       </c>
       <c r="C133" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D133" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E133" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F133" t="s">
-        <v>20</v>
+        <v>326</v>
       </c>
       <c r="G133" t="s">
-        <v>20</v>
+        <v>326</v>
       </c>
       <c r="H133" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>291</v>
+        <v>327</v>
       </c>
       <c r="B134" t="s">
         <v>9</v>
       </c>
       <c r="C134" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D134" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E134" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F134" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G134" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H134" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="B135" t="s">
         <v>9</v>
@@ -5038,24 +5224,24 @@
         <v>10</v>
       </c>
       <c r="D135" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E135" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F135" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G135" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H135" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="B136" t="s">
         <v>9</v>
@@ -5067,47 +5253,47 @@
         <v>11</v>
       </c>
       <c r="E136" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F136" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G136" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H136" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="B137" t="s">
         <v>9</v>
       </c>
       <c r="C137" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D137" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E137" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F137" t="s">
-        <v>20</v>
+        <v>332</v>
       </c>
       <c r="G137" t="s">
-        <v>20</v>
+        <v>332</v>
       </c>
       <c r="H137" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>296</v>
+        <v>333</v>
       </c>
       <c r="B138" t="s">
         <v>9</v>
@@ -5128,12 +5314,12 @@
         <v>14</v>
       </c>
       <c r="H138" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>297</v>
+        <v>334</v>
       </c>
       <c r="B139" t="s">
         <v>9</v>
@@ -5145,21 +5331,21 @@
         <v>11</v>
       </c>
       <c r="E139" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F139" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G139" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H139" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>298</v>
+        <v>335</v>
       </c>
       <c r="B140" t="s">
         <v>9</v>
@@ -5168,24 +5354,24 @@
         <v>10</v>
       </c>
       <c r="D140" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E140" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F140" t="s">
-        <v>299</v>
+        <v>336</v>
       </c>
       <c r="G140" t="s">
-        <v>300</v>
+        <v>337</v>
       </c>
       <c r="H140" t="s">
-        <v>301</v>
+        <v>338</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="B141" t="s">
         <v>9</v>
@@ -5197,47 +5383,47 @@
         <v>11</v>
       </c>
       <c r="E141" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F141" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G141" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H141" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>303</v>
+        <v>340</v>
       </c>
       <c r="B142" t="s">
         <v>9</v>
       </c>
       <c r="C142" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D142" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E142" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F142" t="s">
-        <v>20</v>
+        <v>341</v>
       </c>
       <c r="G142" t="s">
-        <v>20</v>
+        <v>341</v>
       </c>
       <c r="H142" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="B143" t="s">
         <v>9</v>
@@ -5249,21 +5435,21 @@
         <v>11</v>
       </c>
       <c r="E143" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F143" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G143" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H143" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>305</v>
+        <v>343</v>
       </c>
       <c r="B144" t="s">
         <v>9</v>
@@ -5272,24 +5458,24 @@
         <v>10</v>
       </c>
       <c r="D144" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E144" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F144" t="s">
-        <v>20</v>
+        <v>344</v>
       </c>
       <c r="G144" t="s">
-        <v>20</v>
+        <v>344</v>
       </c>
       <c r="H144" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>306</v>
+        <v>345</v>
       </c>
       <c r="B145" t="s">
         <v>9</v>
@@ -5301,21 +5487,21 @@
         <v>11</v>
       </c>
       <c r="E145" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F145" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G145" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H145" t="s">
-        <v>307</v>
+        <v>346</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>308</v>
+        <v>347</v>
       </c>
       <c r="B146" t="s">
         <v>9</v>
@@ -5327,73 +5513,73 @@
         <v>11</v>
       </c>
       <c r="E146" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F146" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G146" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H146" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>309</v>
+        <v>348</v>
       </c>
       <c r="B147" t="s">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="C147" t="s">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="D147" t="s">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="E147" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="F147" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="G147" t="s">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="H147" t="s">
-        <v>20</v>
+        <v>349</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="B148" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C148" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D148" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E148" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F148" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G148" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H148" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>311</v>
+        <v>351</v>
       </c>
       <c r="B149" t="s">
         <v>9</v>
@@ -5402,24 +5588,24 @@
         <v>10</v>
       </c>
       <c r="D149" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="E149" t="s">
-        <v>312</v>
+        <v>352</v>
       </c>
       <c r="F149" t="s">
-        <v>313</v>
+        <v>353</v>
       </c>
       <c r="G149" t="s">
-        <v>314</v>
+        <v>354</v>
       </c>
       <c r="H149" t="s">
-        <v>315</v>
+        <v>355</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="B150" t="s">
         <v>9</v>
@@ -5431,21 +5617,21 @@
         <v>11</v>
       </c>
       <c r="E150" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F150" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G150" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H150" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="B151" t="s">
         <v>9</v>
@@ -5454,24 +5640,24 @@
         <v>10</v>
       </c>
       <c r="D151" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E151" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F151" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="G151" t="s">
-        <v>20</v>
+        <v>358</v>
       </c>
       <c r="H151" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
       <c r="B152" t="s">
         <v>9</v>
@@ -5480,76 +5666,76 @@
         <v>10</v>
       </c>
       <c r="D152" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E152" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F152" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G152" t="s">
-        <v>319</v>
+        <v>360</v>
       </c>
       <c r="H152" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>320</v>
+        <v>361</v>
       </c>
       <c r="B153" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C153" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D153" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E153" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F153" t="s">
-        <v>20</v>
+        <v>362</v>
       </c>
       <c r="G153" t="s">
-        <v>20</v>
+        <v>362</v>
       </c>
       <c r="H153" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>321</v>
+        <v>363</v>
       </c>
       <c r="B154" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C154" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D154" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E154" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F154" t="s">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="G154" t="s">
-        <v>20</v>
+        <v>364</v>
       </c>
       <c r="H154" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>322</v>
+        <v>365</v>
       </c>
       <c r="B155" t="s">
         <v>9</v>
@@ -5558,24 +5744,24 @@
         <v>10</v>
       </c>
       <c r="D155" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E155" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F155" t="s">
-        <v>20</v>
+        <v>366</v>
       </c>
       <c r="G155" t="s">
-        <v>20</v>
+        <v>366</v>
       </c>
       <c r="H155" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>323</v>
+        <v>367</v>
       </c>
       <c r="B156" t="s">
         <v>9</v>
@@ -5584,50 +5770,50 @@
         <v>10</v>
       </c>
       <c r="D156" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E156" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F156" t="s">
-        <v>324</v>
+        <v>368</v>
       </c>
       <c r="G156" t="s">
-        <v>325</v>
+        <v>369</v>
       </c>
       <c r="H156" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>326</v>
+        <v>370</v>
       </c>
       <c r="B157" t="s">
         <v>9</v>
       </c>
       <c r="C157" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D157" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="E157" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F157" t="s">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="G157" t="s">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="H157" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="B158" t="s">
         <v>9</v>
@@ -5636,76 +5822,76 @@
         <v>10</v>
       </c>
       <c r="D158" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="E158" t="s">
-        <v>312</v>
+        <v>352</v>
       </c>
       <c r="F158" t="s">
-        <v>20</v>
+        <v>373</v>
       </c>
       <c r="G158" t="s">
-        <v>20</v>
+        <v>373</v>
       </c>
       <c r="H158" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>328</v>
+        <v>374</v>
       </c>
       <c r="B159" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C159" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D159" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E159" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F159" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G159" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H159" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="B160" t="s">
         <v>9</v>
       </c>
       <c r="C160" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D160" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E160" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F160" t="s">
-        <v>20</v>
+        <v>376</v>
       </c>
       <c r="G160" t="s">
-        <v>20</v>
+        <v>376</v>
       </c>
       <c r="H160" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>330</v>
+        <v>377</v>
       </c>
       <c r="B161" t="s">
         <v>9</v>
@@ -5717,21 +5903,21 @@
         <v>11</v>
       </c>
       <c r="E161" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F161" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G161" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H161" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>331</v>
+        <v>378</v>
       </c>
       <c r="B162" t="s">
         <v>9</v>
@@ -5743,47 +5929,47 @@
         <v>11</v>
       </c>
       <c r="E162" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F162" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G162" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H162" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>332</v>
+        <v>379</v>
       </c>
       <c r="B163" t="s">
         <v>9</v>
       </c>
       <c r="C163" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D163" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E163" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F163" t="s">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="G163" t="s">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="H163" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>333</v>
+        <v>381</v>
       </c>
       <c r="B164" t="s">
         <v>9</v>
@@ -5795,99 +5981,99 @@
         <v>11</v>
       </c>
       <c r="E164" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F164" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G164" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H164" t="s">
-        <v>334</v>
+        <v>382</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>335</v>
+        <v>383</v>
       </c>
       <c r="B165" t="s">
         <v>9</v>
       </c>
       <c r="C165" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="D165" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="E165" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="F165" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="G165" t="s">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="H165" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>336</v>
+        <v>384</v>
       </c>
       <c r="B166" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C166" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D166" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E166" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F166" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G166" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H166" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>337</v>
+        <v>385</v>
       </c>
       <c r="B167" t="s">
         <v>9</v>
       </c>
       <c r="C167" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D167" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E167" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F167" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G167" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H167" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>338</v>
+        <v>386</v>
       </c>
       <c r="B168" t="s">
         <v>9</v>
@@ -5896,24 +6082,24 @@
         <v>10</v>
       </c>
       <c r="D168" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E168" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F168" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G168" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="H168" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="B169" t="s">
         <v>9</v>
@@ -5922,50 +6108,50 @@
         <v>10</v>
       </c>
       <c r="D169" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E169" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F169" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G169" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H169" t="s">
-        <v>340</v>
+        <v>388</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>341</v>
+        <v>389</v>
       </c>
       <c r="B170" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D170" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E170" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F170" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G170" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H170" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>342</v>
+        <v>390</v>
       </c>
       <c r="B171" t="s">
         <v>9</v>
@@ -5977,21 +6163,21 @@
         <v>11</v>
       </c>
       <c r="E171" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F171" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G171" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H171" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>343</v>
+        <v>391</v>
       </c>
       <c r="B172" t="s">
         <v>9</v>
@@ -6000,154 +6186,154 @@
         <v>10</v>
       </c>
       <c r="D172" t="s">
-        <v>11</v>
+        <v>266</v>
       </c>
       <c r="E172" t="s">
-        <v>22</v>
+        <v>392</v>
       </c>
       <c r="F172" t="s">
-        <v>23</v>
+        <v>393</v>
       </c>
       <c r="G172" t="s">
-        <v>24</v>
+        <v>394</v>
       </c>
       <c r="H172" t="s">
-        <v>64</v>
+        <v>395</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>344</v>
+        <v>396</v>
       </c>
       <c r="B173" t="s">
-        <v>9</v>
+        <v>194</v>
       </c>
       <c r="C173" t="s">
-        <v>10</v>
+        <v>195</v>
       </c>
       <c r="D173" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="E173" t="s">
-        <v>345</v>
+        <v>197</v>
       </c>
       <c r="F173" t="s">
-        <v>346</v>
+        <v>198</v>
       </c>
       <c r="G173" t="s">
-        <v>347</v>
+        <v>283</v>
       </c>
       <c r="H173" t="s">
-        <v>348</v>
+        <v>397</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>349</v>
+        <v>398</v>
       </c>
       <c r="B174" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C174" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D174" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E174" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F174" t="s">
-        <v>20</v>
+        <v>399</v>
       </c>
       <c r="G174" t="s">
-        <v>20</v>
+        <v>399</v>
       </c>
       <c r="H174" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="B175" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C175" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D175" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E175" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F175" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G175" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H175" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>351</v>
+        <v>401</v>
       </c>
       <c r="B176" t="s">
-        <v>9</v>
+        <v>402</v>
       </c>
       <c r="C176" t="s">
-        <v>10</v>
+        <v>403</v>
       </c>
       <c r="D176" t="s">
-        <v>11</v>
+        <v>404</v>
       </c>
       <c r="E176" t="s">
-        <v>22</v>
+        <v>405</v>
       </c>
       <c r="F176" t="s">
-        <v>23</v>
+        <v>406</v>
       </c>
       <c r="G176" t="s">
-        <v>24</v>
+        <v>407</v>
       </c>
       <c r="H176" t="s">
-        <v>64</v>
+        <v>408</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>352</v>
+        <v>409</v>
       </c>
       <c r="B177" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C177" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D177" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E177" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F177" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G177" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H177" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>353</v>
+        <v>410</v>
       </c>
       <c r="B178" t="s">
         <v>9</v>
@@ -6156,76 +6342,76 @@
         <v>10</v>
       </c>
       <c r="D178" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E178" t="s">
-        <v>28</v>
+        <v>239</v>
       </c>
       <c r="F178" t="s">
-        <v>29</v>
+        <v>240</v>
       </c>
       <c r="G178" t="s">
-        <v>30</v>
+        <v>241</v>
       </c>
       <c r="H178" t="s">
-        <v>20</v>
+        <v>242</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="B179" t="s">
         <v>9</v>
       </c>
       <c r="C179" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D179" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E179" t="s">
-        <v>213</v>
+        <v>89</v>
       </c>
       <c r="F179" t="s">
-        <v>214</v>
+        <v>412</v>
       </c>
       <c r="G179" t="s">
-        <v>215</v>
+        <v>413</v>
       </c>
       <c r="H179" t="s">
-        <v>216</v>
+        <v>21</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>355</v>
+        <v>414</v>
       </c>
       <c r="B180" t="s">
         <v>9</v>
       </c>
       <c r="C180" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D180" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="E180" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="F180" t="s">
-        <v>356</v>
+        <v>415</v>
       </c>
       <c r="G180" t="s">
-        <v>357</v>
+        <v>416</v>
       </c>
       <c r="H180" t="s">
-        <v>20</v>
+        <v>417</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>358</v>
+        <v>418</v>
       </c>
       <c r="B181" t="s">
         <v>9</v>
@@ -6234,76 +6420,76 @@
         <v>10</v>
       </c>
       <c r="D181" t="s">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c r="E181" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F181" t="s">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="G181" t="s">
-        <v>360</v>
+        <v>419</v>
       </c>
       <c r="H181" t="s">
-        <v>361</v>
+        <v>21</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>362</v>
+        <v>420</v>
       </c>
       <c r="B182" t="s">
         <v>9</v>
       </c>
       <c r="C182" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D182" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="E182" t="s">
-        <v>20</v>
+        <v>421</v>
       </c>
       <c r="F182" t="s">
-        <v>20</v>
+        <v>422</v>
       </c>
       <c r="G182" t="s">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="H182" t="s">
-        <v>20</v>
+        <v>424</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>363</v>
+        <v>425</v>
       </c>
       <c r="B183" t="s">
         <v>9</v>
       </c>
       <c r="C183" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D183" t="s">
-        <v>168</v>
+        <v>11</v>
       </c>
       <c r="E183" t="s">
-        <v>364</v>
+        <v>23</v>
       </c>
       <c r="F183" t="s">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="G183" t="s">
-        <v>366</v>
+        <v>25</v>
       </c>
       <c r="H183" t="s">
-        <v>367</v>
+        <v>74</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>368</v>
+        <v>426</v>
       </c>
       <c r="B184" t="s">
         <v>9</v>
@@ -6315,47 +6501,47 @@
         <v>11</v>
       </c>
       <c r="E184" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F184" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G184" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H184" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>369</v>
+        <v>427</v>
       </c>
       <c r="B185" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C185" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D185" t="s">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="E185" t="s">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="F185" t="s">
-        <v>20</v>
+        <v>268</v>
       </c>
       <c r="G185" t="s">
-        <v>20</v>
+        <v>428</v>
       </c>
       <c r="H185" t="s">
-        <v>20</v>
+        <v>429</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="B186" t="s">
         <v>9</v>
@@ -6364,24 +6550,24 @@
         <v>10</v>
       </c>
       <c r="D186" t="s">
-        <v>239</v>
+        <v>28</v>
       </c>
       <c r="E186" t="s">
-        <v>240</v>
+        <v>21</v>
       </c>
       <c r="F186" t="s">
-        <v>241</v>
+        <v>431</v>
       </c>
       <c r="G186" t="s">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="H186" t="s">
-        <v>372</v>
+        <v>21</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="B187" t="s">
         <v>9</v>
@@ -6390,258 +6576,258 @@
         <v>10</v>
       </c>
       <c r="D187" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E187" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F187" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G187" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H187" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>374</v>
+        <v>433</v>
       </c>
       <c r="B188" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C188" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D188" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E188" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F188" t="s">
-        <v>20</v>
+        <v>434</v>
       </c>
       <c r="G188" t="s">
-        <v>20</v>
+        <v>434</v>
       </c>
       <c r="H188" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>375</v>
+        <v>435</v>
       </c>
       <c r="B189" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C189" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D189" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E189" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="F189" t="s">
-        <v>20</v>
+        <v>436</v>
       </c>
       <c r="G189" t="s">
-        <v>20</v>
+        <v>436</v>
       </c>
       <c r="H189" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>376</v>
+        <v>437</v>
       </c>
       <c r="B190" t="s">
         <v>9</v>
       </c>
       <c r="C190" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D190" t="s">
-        <v>41</v>
+        <v>438</v>
       </c>
       <c r="E190" t="s">
-        <v>42</v>
+        <v>439</v>
       </c>
       <c r="F190" t="s">
-        <v>20</v>
+        <v>440</v>
       </c>
       <c r="G190" t="s">
-        <v>20</v>
+        <v>441</v>
       </c>
       <c r="H190" t="s">
-        <v>20</v>
+        <v>442</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>377</v>
+        <v>443</v>
       </c>
       <c r="B191" t="s">
         <v>9</v>
       </c>
       <c r="C191" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D191" t="s">
-        <v>378</v>
+        <v>11</v>
       </c>
       <c r="E191" t="s">
-        <v>379</v>
+        <v>23</v>
       </c>
       <c r="F191" t="s">
-        <v>380</v>
+        <v>24</v>
       </c>
       <c r="G191" t="s">
-        <v>381</v>
+        <v>25</v>
       </c>
       <c r="H191" t="s">
-        <v>382</v>
+        <v>21</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>383</v>
+        <v>444</v>
       </c>
       <c r="B192" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C192" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D192" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E192" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="F192" t="s">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="G192" t="s">
-        <v>20</v>
+        <v>445</v>
       </c>
       <c r="H192" t="s">
-        <v>20</v>
+        <v>446</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>384</v>
+        <v>447</v>
       </c>
       <c r="B193" t="s">
         <v>9</v>
       </c>
       <c r="C193" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D193" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="E193" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="F193" t="s">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="G193" t="s">
-        <v>385</v>
+        <v>25</v>
       </c>
       <c r="H193" t="s">
-        <v>386</v>
+        <v>448</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>387</v>
+        <v>449</v>
       </c>
       <c r="B194" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C194" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D194" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E194" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F194" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G194" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H194" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>388</v>
+        <v>450</v>
       </c>
       <c r="B195" t="s">
         <v>9</v>
       </c>
       <c r="C195" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D195" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E195" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F195" t="s">
-        <v>23</v>
+        <v>451</v>
       </c>
       <c r="G195" t="s">
-        <v>24</v>
+        <v>451</v>
       </c>
       <c r="H195" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>389</v>
+        <v>452</v>
       </c>
       <c r="B196" t="s">
         <v>9</v>
       </c>
       <c r="C196" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D196" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E196" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F196" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G196" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H196" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>390</v>
+        <v>453</v>
       </c>
       <c r="B197" t="s">
         <v>9</v>
@@ -6653,224 +6839,198 @@
         <v>11</v>
       </c>
       <c r="E197" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F197" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G197" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H197" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>391</v>
+        <v>454</v>
       </c>
       <c r="B198" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C198" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D198" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="E198" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="F198" t="s">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="G198" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="H198" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>392</v>
+        <v>455</v>
       </c>
       <c r="B199" t="s">
         <v>9</v>
       </c>
       <c r="C199" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D199" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="E199" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="F199" t="s">
-        <v>134</v>
+        <v>24</v>
       </c>
       <c r="G199" t="s">
-        <v>135</v>
+        <v>25</v>
       </c>
       <c r="H199" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>393</v>
+        <v>456</v>
       </c>
       <c r="B200" t="s">
         <v>9</v>
       </c>
       <c r="C200" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D200" t="s">
-        <v>11</v>
+        <v>438</v>
       </c>
       <c r="E200" t="s">
-        <v>22</v>
+        <v>439</v>
       </c>
       <c r="F200" t="s">
-        <v>23</v>
+        <v>440</v>
       </c>
       <c r="G200" t="s">
-        <v>24</v>
+        <v>441</v>
       </c>
       <c r="H200" t="s">
-        <v>68</v>
+        <v>457</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="B201" t="s">
         <v>9</v>
       </c>
       <c r="C201" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D201" t="s">
-        <v>378</v>
+        <v>28</v>
       </c>
       <c r="E201" t="s">
-        <v>379</v>
+        <v>103</v>
       </c>
       <c r="F201" t="s">
-        <v>380</v>
+        <v>104</v>
       </c>
       <c r="G201" t="s">
-        <v>381</v>
+        <v>105</v>
       </c>
       <c r="H201" t="s">
-        <v>395</v>
+        <v>233</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>396</v>
+        <v>459</v>
       </c>
       <c r="B202" t="s">
         <v>9</v>
       </c>
       <c r="C202" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D202" t="s">
-        <v>27</v>
+        <v>438</v>
       </c>
       <c r="E202" t="s">
-        <v>96</v>
+        <v>439</v>
       </c>
       <c r="F202" t="s">
-        <v>97</v>
+        <v>440</v>
       </c>
       <c r="G202" t="s">
-        <v>98</v>
+        <v>441</v>
       </c>
       <c r="H202" t="s">
-        <v>207</v>
+        <v>457</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>397</v>
+        <v>460</v>
       </c>
       <c r="B203" t="s">
         <v>9</v>
       </c>
       <c r="C203" t="s">
-        <v>33</v>
+        <v>301</v>
       </c>
       <c r="D203" t="s">
-        <v>378</v>
+        <v>302</v>
       </c>
       <c r="E203" t="s">
-        <v>379</v>
+        <v>303</v>
       </c>
       <c r="F203" t="s">
-        <v>380</v>
+        <v>304</v>
       </c>
       <c r="G203" t="s">
-        <v>381</v>
+        <v>305</v>
       </c>
       <c r="H203" t="s">
-        <v>395</v>
+        <v>21</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>398</v>
+        <v>461</v>
       </c>
       <c r="B204" t="s">
         <v>9</v>
       </c>
       <c r="C204" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="D204" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="E204" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="F204" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="G204" t="s">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="H204" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="s">
-        <v>399</v>
-      </c>
-      <c r="B205" t="s">
-        <v>9</v>
-      </c>
-      <c r="C205" t="s">
-        <v>269</v>
-      </c>
-      <c r="D205" t="s">
-        <v>270</v>
-      </c>
-      <c r="E205" t="s">
-        <v>271</v>
-      </c>
-      <c r="F205" t="s">
-        <v>272</v>
-      </c>
-      <c r="G205" t="s">
-        <v>273</v>
-      </c>
-      <c r="H205" t="s">
-        <v>400</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
